--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -978,11 +978,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1118,11 +1114,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1258,11 +1250,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1398,11 +1386,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1538,11 +1522,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1678,11 +1658,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1818,11 +1794,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1958,11 +1930,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2098,11 +2066,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2238,11 +2202,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2378,11 +2338,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2518,11 +2474,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2658,11 +2610,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2798,11 +2746,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2938,11 +2882,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 28741-2023 artfynd.xlsx
+++ b/artfynd/A 28741-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172145</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137172146</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137172096</v>
       </c>
       <c r="B4" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>137172097</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>137172098</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>137172099</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>137172100</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>137172101</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>137172102</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137172103</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         <v>137172104</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>137172105</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>137172106</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>137172107</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>137172108</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>137172109</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>137172110</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
